--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_arica_y_parinacota.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:44</t>
+    <t xml:space="preserve">2026-09-24 00:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -761,7 +761,7 @@
         <v>-0.77</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19">
@@ -775,7 +775,7 @@
         <v>-0.22</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="20">
@@ -789,7 +789,7 @@
         <v>-0.66</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="21">
@@ -803,7 +803,7 @@
         <v>-0.41</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_arica_y_parinacota.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:35</t>
+    <t xml:space="preserve">2026-10-01 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2018_arica_y_parinacota.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:06</t>
+    <t xml:space="preserve">2026-10-05 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
